--- a/data/coding/coder2/P16.xlsx
+++ b/data/coding/coder2/P16.xlsx
@@ -1290,11 +1290,11 @@
       </c>
       <c r="E27" s="5" t="inlineStr">
         <is>
-          <t>아하 ㅋㅋㅋ 그럼 어머니가 발견하시고 태은이가 구조대 역할을 한 거네 😆 사진 보니까 진짜 조심스럽게 옮겨준 것 같아.</t>
+          <t>아하 ㅋㅋㅋ 그럼 어머니가 발견하시고 [이름]이가 구조대 역할을 한 거네 😆 사진 보니까 진짜 조심스럽게 옮겨준 것 같아.</t>
         </is>
       </c>
       <c r="F27" s="4" t="n">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="G27" s="6" t="inlineStr"/>
       <c r="H27" s="6" t="inlineStr"/>
@@ -1402,11 +1402,11 @@
       </c>
       <c r="E31" s="5" t="inlineStr">
         <is>
-          <t>그리고 솔직히 말하면... 부추에서 민달팽이 나오면 무서워서 소리 지르거나 바로 버리는 사람도 많은데 😅 태은이는 직접 옮겨줬으니 그 친구는 운이 좋았네.</t>
+          <t>그리고 솔직히 말하면... 부추에서 민달팽이 나오면 무서워서 소리 지르거나 바로 버리는 사람도 많은데 😅 [이름]이는 직접 옮겨줬으니 그 친구는 운이 좋았네.</t>
         </is>
       </c>
       <c r="F31" s="4" t="n">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="G31" s="6" t="inlineStr"/>
       <c r="H31" s="6" t="inlineStr"/>
@@ -1552,11 +1552,11 @@
       </c>
       <c r="E36" s="8" t="inlineStr">
         <is>
-          <t>민달팽이도 무사히 나무에 붙어 있었고, 비도 와서 촉촉한 환경이라 잘 지낼 거야 🌿🐌 그리고 뭔가 태은이는 벌레나 작은 생물을 발견하면 무서워하면서도 그냥 못 지나치는 타입인 것 같아 ㅋㅋㅋ 토요일에 서포터즈 가는 것도 잘 다녀오고!</t>
+          <t>민달팽이도 무사히 나무에 붙어 있었고, 비도 와서 촉촉한 환경이라 잘 지낼 거야 🌿🐌 그리고 뭔가 [이름]이는 벌레나 작은 생물을 발견하면 무서워하면서도 그냥 못 지나치는 타입인 것 같아 ㅋㅋㅋ 토요일에 서포터즈 가는 것도 잘 다녀오고!</t>
         </is>
       </c>
       <c r="F36" s="7" t="n">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="G36" s="6" t="inlineStr"/>
       <c r="H36" s="6" t="inlineStr"/>
